--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_d_residentes_a_2018.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_d_residentes_a_2018.xlsx
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:43</t>
+    <t xml:space="preserve">2026-09-24 00:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_d_residentes_a_2018.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_d_residentes_a_2018.xlsx
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:34</t>
+    <t xml:space="preserve">2026-10-01 23:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_d_residentes_a_2018.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_d_residentes_a_2018.xlsx
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:05</t>
+    <t xml:space="preserve">2026-10-05 19:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
